--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/2026 Giro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7029055-D8C6-43FA-9D5A-F006E77F34CC}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53E7573D-5D53-452F-BA3A-3308E3D0B465}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="161">
   <si>
     <t>Stage</t>
   </si>
@@ -483,13 +483,52 @@
   </si>
   <si>
     <t>Michael Storer</t>
+  </si>
+  <si>
+    <t>GC #1</t>
+  </si>
+  <si>
+    <t>GC #2</t>
+  </si>
+  <si>
+    <t>GC #3</t>
+  </si>
+  <si>
+    <t>GC #4</t>
+  </si>
+  <si>
+    <t>GC #5</t>
+  </si>
+  <si>
+    <t>GC #6</t>
+  </si>
+  <si>
+    <t>GC #7</t>
+  </si>
+  <si>
+    <t>GC #8</t>
+  </si>
+  <si>
+    <t>GC #9</t>
+  </si>
+  <si>
+    <t>GC #10</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>Mountains</t>
+  </si>
+  <si>
+    <t>Young Rider</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,6 +542,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -512,7 +559,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -520,13 +567,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -861,22 +926,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -913,8 +991,47 @@
       <c r="L1" t="s">
         <v>10</v>
       </c>
+      <c r="M1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O1" t="s">
+        <v>150</v>
+      </c>
+      <c r="P1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>152</v>
+      </c>
+      <c r="R1" t="s">
+        <v>153</v>
+      </c>
+      <c r="S1" t="s">
+        <v>154</v>
+      </c>
+      <c r="T1" t="s">
+        <v>155</v>
+      </c>
+      <c r="U1" t="s">
+        <v>156</v>
+      </c>
+      <c r="V1" t="s">
+        <v>157</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>160</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2">
         <v>1</v>
@@ -949,8 +1066,47 @@
       <c r="L2" t="s">
         <v>36</v>
       </c>
+      <c r="M2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" t="s">
+        <v>103</v>
+      </c>
+      <c r="X2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3">
         <v>2</v>
@@ -985,8 +1141,47 @@
       <c r="L3" t="s">
         <v>20</v>
       </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" t="s">
+        <v>103</v>
+      </c>
+      <c r="X3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4">
         <v>3</v>
@@ -1021,8 +1216,47 @@
       <c r="L4" t="s">
         <v>30</v>
       </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U4" t="s">
+        <v>35</v>
+      </c>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" t="s">
+        <v>103</v>
+      </c>
+      <c r="X4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5">
         <v>4</v>
@@ -1057,8 +1291,47 @@
       <c r="L5" t="s">
         <v>36</v>
       </c>
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U5" t="s">
+        <v>35</v>
+      </c>
+      <c r="V5" t="s">
+        <v>36</v>
+      </c>
+      <c r="W5" t="s">
+        <v>103</v>
+      </c>
+      <c r="X5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6">
         <v>5</v>
@@ -1093,8 +1366,47 @@
       <c r="L6" t="s">
         <v>33</v>
       </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" t="s">
+        <v>34</v>
+      </c>
+      <c r="T6" t="s">
+        <v>19</v>
+      </c>
+      <c r="U6" t="s">
+        <v>35</v>
+      </c>
+      <c r="V6" t="s">
+        <v>36</v>
+      </c>
+      <c r="W6" t="s">
+        <v>103</v>
+      </c>
+      <c r="X6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7">
         <v>6</v>
@@ -1129,8 +1441,47 @@
       <c r="L7" t="s">
         <v>50</v>
       </c>
+      <c r="M7" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" t="s">
+        <v>34</v>
+      </c>
+      <c r="T7" t="s">
+        <v>19</v>
+      </c>
+      <c r="U7" t="s">
+        <v>35</v>
+      </c>
+      <c r="V7" t="s">
+        <v>36</v>
+      </c>
+      <c r="W7" t="s">
+        <v>103</v>
+      </c>
+      <c r="X7" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8">
         <v>7</v>
@@ -1165,8 +1516,47 @@
       <c r="L8" t="s">
         <v>40</v>
       </c>
+      <c r="M8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T8" t="s">
+        <v>19</v>
+      </c>
+      <c r="U8" t="s">
+        <v>35</v>
+      </c>
+      <c r="V8" t="s">
+        <v>36</v>
+      </c>
+      <c r="W8" t="s">
+        <v>103</v>
+      </c>
+      <c r="X8" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9">
         <v>8</v>
@@ -1201,8 +1591,47 @@
       <c r="L9" t="s">
         <v>62</v>
       </c>
+      <c r="M9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>33</v>
+      </c>
+      <c r="R9" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9" t="s">
+        <v>34</v>
+      </c>
+      <c r="T9" t="s">
+        <v>19</v>
+      </c>
+      <c r="U9" t="s">
+        <v>35</v>
+      </c>
+      <c r="V9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W9" t="s">
+        <v>103</v>
+      </c>
+      <c r="X9" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10">
         <v>9</v>
@@ -1237,8 +1666,47 @@
       <c r="L10" t="s">
         <v>71</v>
       </c>
+      <c r="M10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" t="s">
+        <v>34</v>
+      </c>
+      <c r="T10" t="s">
+        <v>19</v>
+      </c>
+      <c r="U10" t="s">
+        <v>35</v>
+      </c>
+      <c r="V10" t="s">
+        <v>36</v>
+      </c>
+      <c r="W10" t="s">
+        <v>103</v>
+      </c>
+      <c r="X10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11">
         <v>10</v>
@@ -1273,8 +1741,47 @@
       <c r="L11" t="s">
         <v>57</v>
       </c>
+      <c r="M11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>33</v>
+      </c>
+      <c r="R11" t="s">
+        <v>23</v>
+      </c>
+      <c r="S11" t="s">
+        <v>34</v>
+      </c>
+      <c r="T11" t="s">
+        <v>19</v>
+      </c>
+      <c r="U11" t="s">
+        <v>35</v>
+      </c>
+      <c r="V11" t="s">
+        <v>36</v>
+      </c>
+      <c r="W11" t="s">
+        <v>103</v>
+      </c>
+      <c r="X11" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12">
         <v>11</v>
@@ -1309,8 +1816,47 @@
       <c r="L12" t="s">
         <v>81</v>
       </c>
+      <c r="M12" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>33</v>
+      </c>
+      <c r="R12" t="s">
+        <v>23</v>
+      </c>
+      <c r="S12" t="s">
+        <v>34</v>
+      </c>
+      <c r="T12" t="s">
+        <v>19</v>
+      </c>
+      <c r="U12" t="s">
+        <v>35</v>
+      </c>
+      <c r="V12" t="s">
+        <v>36</v>
+      </c>
+      <c r="W12" t="s">
+        <v>103</v>
+      </c>
+      <c r="X12" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13">
         <v>12</v>
@@ -1345,8 +1891,47 @@
       <c r="L13" t="s">
         <v>57</v>
       </c>
+      <c r="M13" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>33</v>
+      </c>
+      <c r="R13" t="s">
+        <v>23</v>
+      </c>
+      <c r="S13" t="s">
+        <v>34</v>
+      </c>
+      <c r="T13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U13" t="s">
+        <v>35</v>
+      </c>
+      <c r="V13" t="s">
+        <v>36</v>
+      </c>
+      <c r="W13" t="s">
+        <v>103</v>
+      </c>
+      <c r="X13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14">
         <v>13</v>
@@ -1381,8 +1966,47 @@
       <c r="L14" t="s">
         <v>94</v>
       </c>
+      <c r="M14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" t="s">
+        <v>15</v>
+      </c>
+      <c r="O14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>33</v>
+      </c>
+      <c r="R14" t="s">
+        <v>23</v>
+      </c>
+      <c r="S14" t="s">
+        <v>34</v>
+      </c>
+      <c r="T14" t="s">
+        <v>19</v>
+      </c>
+      <c r="U14" t="s">
+        <v>35</v>
+      </c>
+      <c r="V14" t="s">
+        <v>36</v>
+      </c>
+      <c r="W14" t="s">
+        <v>103</v>
+      </c>
+      <c r="X14" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15">
         <v>14</v>
@@ -1417,8 +2041,47 @@
       <c r="L15" t="s">
         <v>102</v>
       </c>
+      <c r="M15" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" t="s">
+        <v>15</v>
+      </c>
+      <c r="O15" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>33</v>
+      </c>
+      <c r="R15" t="s">
+        <v>23</v>
+      </c>
+      <c r="S15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T15" t="s">
+        <v>19</v>
+      </c>
+      <c r="U15" t="s">
+        <v>35</v>
+      </c>
+      <c r="V15" t="s">
+        <v>36</v>
+      </c>
+      <c r="W15" t="s">
+        <v>103</v>
+      </c>
+      <c r="X15" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16">
         <v>15</v>
@@ -1453,8 +2116,47 @@
       <c r="L16" t="s">
         <v>99</v>
       </c>
+      <c r="M16" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" t="s">
+        <v>15</v>
+      </c>
+      <c r="O16" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" t="s">
+        <v>23</v>
+      </c>
+      <c r="S16" t="s">
+        <v>34</v>
+      </c>
+      <c r="T16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U16" t="s">
+        <v>35</v>
+      </c>
+      <c r="V16" t="s">
+        <v>36</v>
+      </c>
+      <c r="W16" t="s">
+        <v>103</v>
+      </c>
+      <c r="X16" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17">
         <v>16</v>
@@ -1489,8 +2191,47 @@
       <c r="L17" t="s">
         <v>138</v>
       </c>
+      <c r="M17" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" t="s">
+        <v>15</v>
+      </c>
+      <c r="O17" t="s">
+        <v>32</v>
+      </c>
+      <c r="P17" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>33</v>
+      </c>
+      <c r="R17" t="s">
+        <v>23</v>
+      </c>
+      <c r="S17" t="s">
+        <v>34</v>
+      </c>
+      <c r="T17" t="s">
+        <v>19</v>
+      </c>
+      <c r="U17" t="s">
+        <v>35</v>
+      </c>
+      <c r="V17" t="s">
+        <v>36</v>
+      </c>
+      <c r="W17" t="s">
+        <v>103</v>
+      </c>
+      <c r="X17" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18">
         <v>17</v>
@@ -1525,8 +2266,47 @@
       <c r="L18" t="s">
         <v>128</v>
       </c>
+      <c r="M18" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" t="s">
+        <v>15</v>
+      </c>
+      <c r="O18" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>33</v>
+      </c>
+      <c r="R18" t="s">
+        <v>23</v>
+      </c>
+      <c r="S18" t="s">
+        <v>34</v>
+      </c>
+      <c r="T18" t="s">
+        <v>19</v>
+      </c>
+      <c r="U18" t="s">
+        <v>35</v>
+      </c>
+      <c r="V18" t="s">
+        <v>36</v>
+      </c>
+      <c r="W18" t="s">
+        <v>103</v>
+      </c>
+      <c r="X18" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19">
         <v>18</v>
@@ -1561,8 +2341,47 @@
       <c r="L19" t="s">
         <v>137</v>
       </c>
+      <c r="M19" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" t="s">
+        <v>23</v>
+      </c>
+      <c r="S19" t="s">
+        <v>34</v>
+      </c>
+      <c r="T19" t="s">
+        <v>19</v>
+      </c>
+      <c r="U19" t="s">
+        <v>35</v>
+      </c>
+      <c r="V19" t="s">
+        <v>36</v>
+      </c>
+      <c r="W19" t="s">
+        <v>103</v>
+      </c>
+      <c r="X19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20">
         <v>19</v>
@@ -1597,8 +2416,47 @@
       <c r="L20" t="s">
         <v>124</v>
       </c>
+      <c r="M20" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" t="s">
+        <v>15</v>
+      </c>
+      <c r="O20" t="s">
+        <v>32</v>
+      </c>
+      <c r="P20" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>33</v>
+      </c>
+      <c r="R20" t="s">
+        <v>23</v>
+      </c>
+      <c r="S20" t="s">
+        <v>34</v>
+      </c>
+      <c r="T20" t="s">
+        <v>19</v>
+      </c>
+      <c r="U20" t="s">
+        <v>35</v>
+      </c>
+      <c r="V20" t="s">
+        <v>36</v>
+      </c>
+      <c r="W20" t="s">
+        <v>103</v>
+      </c>
+      <c r="X20" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21">
         <v>20</v>
@@ -1633,8 +2491,47 @@
       <c r="L21" t="s">
         <v>77</v>
       </c>
+      <c r="M21" t="s">
+        <v>31</v>
+      </c>
+      <c r="N21" t="s">
+        <v>15</v>
+      </c>
+      <c r="O21" t="s">
+        <v>32</v>
+      </c>
+      <c r="P21" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>33</v>
+      </c>
+      <c r="R21" t="s">
+        <v>23</v>
+      </c>
+      <c r="S21" t="s">
+        <v>34</v>
+      </c>
+      <c r="T21" t="s">
+        <v>19</v>
+      </c>
+      <c r="U21" t="s">
+        <v>35</v>
+      </c>
+      <c r="V21" t="s">
+        <v>36</v>
+      </c>
+      <c r="W21" t="s">
+        <v>103</v>
+      </c>
+      <c r="X21" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22">
         <v>21</v>
@@ -1668,6 +2565,45 @@
       </c>
       <c r="L22" t="s">
         <v>147</v>
+      </c>
+      <c r="M22" t="s">
+        <v>31</v>
+      </c>
+      <c r="N22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O22" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>33</v>
+      </c>
+      <c r="R22" t="s">
+        <v>23</v>
+      </c>
+      <c r="S22" t="s">
+        <v>34</v>
+      </c>
+      <c r="T22" t="s">
+        <v>19</v>
+      </c>
+      <c r="U22" t="s">
+        <v>35</v>
+      </c>
+      <c r="V22" t="s">
+        <v>36</v>
+      </c>
+      <c r="W22" t="s">
+        <v>103</v>
+      </c>
+      <c r="X22" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/2026 Giro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="213" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E7D5F44-783B-42FD-ABA6-9AA30F686725}"/>
+  <xr:revisionPtr revIDLastSave="224" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E3CE12B-08C6-459F-A21B-673566BD751D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="77">
   <si>
     <t>Stage</t>
   </si>
@@ -210,6 +210,63 @@
   </si>
   <si>
     <t>Isaac Del Toro</t>
+  </si>
+  <si>
+    <t>Corbin Strong</t>
+  </si>
+  <si>
+    <t>Brandon Smith Rivera</t>
+  </si>
+  <si>
+    <t>Edoardo Zambanini</t>
+  </si>
+  <si>
+    <t>Stefano Oldani</t>
+  </si>
+  <si>
+    <t>Andrea Vendrame</t>
+  </si>
+  <si>
+    <t>Filippo Fiorelli</t>
+  </si>
+  <si>
+    <t>Christian Scaroni</t>
+  </si>
+  <si>
+    <t>Davide De Pretto</t>
+  </si>
+  <si>
+    <t>Alessandro Tonelli</t>
+  </si>
+  <si>
+    <t>Pello Bilbao</t>
+  </si>
+  <si>
+    <t>Casper van Uden</t>
+  </si>
+  <si>
+    <t>Olav Kooij</t>
+  </si>
+  <si>
+    <t>Maikel Zijlaard</t>
+  </si>
+  <si>
+    <t>Kaden Groves</t>
+  </si>
+  <si>
+    <t>Sam Bennett</t>
+  </si>
+  <si>
+    <t>Paul Magnier</t>
+  </si>
+  <si>
+    <t>Ben Turner</t>
+  </si>
+  <si>
+    <t>Matteo Moschetti</t>
+  </si>
+  <si>
+    <t>Enrico Zanoncello</t>
   </si>
 </sst>
 </file>
@@ -588,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:AE19"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -596,12 +653,11 @@
     <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
@@ -613,10 +669,9 @@
     <col min="21" max="21" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="17" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -909,10 +964,194 @@
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1">
+        <v>45789</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" t="s">
+        <v>17</v>
+      </c>
+      <c r="U4" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" t="s">
+        <v>16</v>
+      </c>
+      <c r="W4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X4" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1">
+        <v>45790</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T5" t="s">
+        <v>17</v>
+      </c>
+      <c r="U5" t="s">
+        <v>22</v>
+      </c>
+      <c r="V5" t="s">
+        <v>16</v>
+      </c>
+      <c r="W5" t="s">
+        <v>33</v>
+      </c>
+      <c r="X5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -952,9 +1191,6 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/2026 Giro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="224" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E3CE12B-08C6-459F-A21B-673566BD751D}"/>
+  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{8C193552-8267-4083-B3AB-168CA7CCEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C4C0C09-3BCF-41DA-9FDC-4C58F56B5E40}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="122">
   <si>
     <t>Stage</t>
   </si>
@@ -164,9 +164,6 @@
     <t>Davide Piganzoli</t>
   </si>
   <si>
-    <t>Sylvain Moniquet</t>
-  </si>
-  <si>
     <t>Points #2</t>
   </si>
   <si>
@@ -194,9 +191,6 @@
     <t>Youth #3</t>
   </si>
   <si>
-    <t>Manuele Tarozzi</t>
-  </si>
-  <si>
     <t>Lorenzo Fortunato</t>
   </si>
   <si>
@@ -236,12 +230,6 @@
     <t>Davide De Pretto</t>
   </si>
   <si>
-    <t>Alessandro Tonelli</t>
-  </si>
-  <si>
-    <t>Pello Bilbao</t>
-  </si>
-  <si>
     <t>Casper van Uden</t>
   </si>
   <si>
@@ -267,6 +255,153 @@
   </si>
   <si>
     <t>Enrico Zanoncello</t>
+  </si>
+  <si>
+    <t>Quentin Pacher</t>
+  </si>
+  <si>
+    <t>Damiano Caruso</t>
+  </si>
+  <si>
+    <t>Luke Plapp</t>
+  </si>
+  <si>
+    <t>Kasper Asgreen</t>
+  </si>
+  <si>
+    <t>Carlos Verona</t>
+  </si>
+  <si>
+    <t>Nico Denz</t>
+  </si>
+  <si>
+    <t>Nicolas Prodhomme</t>
+  </si>
+  <si>
+    <t>Chris Harper</t>
+  </si>
+  <si>
+    <t>Luke Lamperti</t>
+  </si>
+  <si>
+    <t>Max Kanter</t>
+  </si>
+  <si>
+    <t>Filippo Baroncini</t>
+  </si>
+  <si>
+    <t>Giovanni Lonardi</t>
+  </si>
+  <si>
+    <t>Milan Fretin</t>
+  </si>
+  <si>
+    <t>Martin Marcellusi</t>
+  </si>
+  <si>
+    <t>Luca Mozzato</t>
+  </si>
+  <si>
+    <t>Matevž Govekar</t>
+  </si>
+  <si>
+    <t>Egan Bernal</t>
+  </si>
+  <si>
+    <t>Wilco Kelderman</t>
+  </si>
+  <si>
+    <t>Igor Arrieta</t>
+  </si>
+  <si>
+    <t>Georg Steinhauser</t>
+  </si>
+  <si>
+    <t>Romain Bardet</t>
+  </si>
+  <si>
+    <t>Alessio Martinelli</t>
+  </si>
+  <si>
+    <t>Simon Yates</t>
+  </si>
+  <si>
+    <t>Thymen Arensman</t>
+  </si>
+  <si>
+    <t>Adam Yates</t>
+  </si>
+  <si>
+    <t>Mattia Cattaneo</t>
+  </si>
+  <si>
+    <t>Marco Frigo</t>
+  </si>
+  <si>
+    <t>Michael Hepburn</t>
+  </si>
+  <si>
+    <t>Xabier Mikel Azparren</t>
+  </si>
+  <si>
+    <t>Einer Rubio</t>
+  </si>
+  <si>
+    <t>Derek Gee-West</t>
+  </si>
+  <si>
+    <t>Rémy Rochas</t>
+  </si>
+  <si>
+    <t>Dorian Godon</t>
+  </si>
+  <si>
+    <t>Mirco Maestri</t>
+  </si>
+  <si>
+    <t>Mikkel Frølich Honoré</t>
+  </si>
+  <si>
+    <t>Florian Stork</t>
+  </si>
+  <si>
+    <t>Filippo Zana</t>
+  </si>
+  <si>
+    <t>Gianmarco Garofoli</t>
+  </si>
+  <si>
+    <t>Jefferson Alveiro Cepeda</t>
+  </si>
+  <si>
+    <t>Gijs Leemreize</t>
+  </si>
+  <si>
+    <t>Yannis Voisard</t>
+  </si>
+  <si>
+    <t>Afonso Eulálio</t>
+  </si>
+  <si>
+    <t>Edward Planckaert</t>
+  </si>
+  <si>
+    <t>Filippo Magli</t>
+  </si>
+  <si>
+    <t>Alex Edmondson</t>
+  </si>
+  <si>
+    <t>Dries De Bondt</t>
+  </si>
+  <si>
+    <t>Larry Warbasse</t>
+  </si>
+  <si>
+    <t>Rafał Majka</t>
+  </si>
+  <si>
+    <t>Alessandro Verre</t>
   </si>
 </sst>
 </file>
@@ -645,37 +780,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AE22"/>
   <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="17" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -746,31 +884,31 @@
         <v>32</v>
       </c>
       <c r="W1" t="s">
+        <v>43</v>
+      </c>
+      <c r="X1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y1" t="s">
         <v>44</v>
       </c>
-      <c r="X1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>45</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>46</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>47</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>48</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>49</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>50</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -810,63 +948,6 @@
       <c r="L2" t="s">
         <v>41</v>
       </c>
-      <c r="M2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" t="s">
-        <v>39</v>
-      </c>
-      <c r="U2" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -879,13 +960,13 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
@@ -904,63 +985,6 @@
       </c>
       <c r="L3" t="s">
         <v>21</v>
-      </c>
-      <c r="M3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N3" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R3" t="s">
-        <v>57</v>
-      </c>
-      <c r="S3" t="s">
-        <v>39</v>
-      </c>
-      <c r="T3" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" t="s">
-        <v>22</v>
-      </c>
-      <c r="V3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W3" t="s">
-        <v>33</v>
-      </c>
-      <c r="X3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
@@ -974,88 +998,31 @@
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>35</v>
       </c>
       <c r="F4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" t="s">
         <v>59</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>60</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>61</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>62</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>63</v>
-      </c>
-      <c r="K4" t="s">
-        <v>64</v>
-      </c>
-      <c r="L4" t="s">
-        <v>65</v>
-      </c>
-      <c r="M4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S4" t="s">
-        <v>39</v>
-      </c>
-      <c r="T4" t="s">
-        <v>17</v>
-      </c>
-      <c r="U4" t="s">
-        <v>22</v>
-      </c>
-      <c r="V4" t="s">
-        <v>16</v>
-      </c>
-      <c r="W4" t="s">
-        <v>33</v>
-      </c>
-      <c r="X4" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
@@ -1066,131 +1033,738 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F5" t="s">
         <v>33</v>
       </c>
       <c r="G5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" t="s">
         <v>71</v>
       </c>
-      <c r="H5" t="s">
+      <c r="L5" t="s">
         <v>72</v>
       </c>
-      <c r="I5" t="s">
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>45791</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
         <v>73</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" t="s">
         <v>74</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45792</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>45793</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>45794</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>75</v>
       </c>
-      <c r="L5" t="s">
+      <c r="D9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
+        <v>92</v>
+      </c>
+      <c r="K9" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>45795</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>45797</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" t="s">
+        <v>100</v>
+      </c>
+      <c r="L11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>45798</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>45800</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>103</v>
+      </c>
+      <c r="K14" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>45801</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
         <v>76</v>
       </c>
-      <c r="M5" t="s">
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" t="s">
+        <v>103</v>
+      </c>
+      <c r="J15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>45802</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J16" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>45804</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" t="s">
+        <v>95</v>
+      </c>
+      <c r="K17" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>45805</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" t="s">
+        <v>103</v>
+      </c>
+      <c r="I18" t="s">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s">
+        <v>102</v>
+      </c>
+      <c r="K18" t="s">
+        <v>39</v>
+      </c>
+      <c r="L18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" t="s">
+        <v>118</v>
+      </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" t="s">
+        <v>63</v>
+      </c>
+      <c r="K19" t="s">
+        <v>40</v>
+      </c>
+      <c r="L19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>45807</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>89</v>
+      </c>
+      <c r="I20" t="s">
+        <v>95</v>
+      </c>
+      <c r="J20" t="s">
+        <v>120</v>
+      </c>
+      <c r="K20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>45808</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" t="s">
+        <v>77</v>
+      </c>
+      <c r="J21" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21" t="s">
+        <v>55</v>
+      </c>
+      <c r="L21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" t="s">
         <v>33</v>
       </c>
-      <c r="N5" t="s">
+      <c r="G22" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" t="s">
+        <v>83</v>
+      </c>
+      <c r="J22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" t="s">
+        <v>84</v>
+      </c>
+      <c r="M22" t="s">
+        <v>95</v>
+      </c>
+      <c r="N22" t="s">
         <v>55</v>
       </c>
-      <c r="O5" t="s">
-        <v>14</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="O22" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>74</v>
+      </c>
+      <c r="R22" t="s">
+        <v>16</v>
+      </c>
+      <c r="S22" t="s">
+        <v>89</v>
+      </c>
+      <c r="T22" t="s">
+        <v>102</v>
+      </c>
+      <c r="U22" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" t="s">
-        <v>57</v>
-      </c>
-      <c r="R5" t="s">
-        <v>21</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="V22" t="s">
+        <v>22</v>
+      </c>
+      <c r="W22" t="s">
+        <v>33</v>
+      </c>
+      <c r="X22" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE22" t="s">
         <v>39</v>
       </c>
-      <c r="T5" t="s">
-        <v>17</v>
-      </c>
-      <c r="U5" t="s">
-        <v>22</v>
-      </c>
-      <c r="V5" t="s">
-        <v>16</v>
-      </c>
-      <c r="W5" t="s">
-        <v>33</v>
-      </c>
-      <c r="X5" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
